--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131734526</v>
+        <v>135468092</v>
       </c>
       <c r="B3" t="n">
-        <v>97471</v>
+        <v>91985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stögölen Nord, Ög</t>
+          <t>Stögölen, Stögölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569603</v>
+        <v>569568</v>
       </c>
       <c r="R3" t="n">
-        <v>6511533</v>
+        <v>6511572</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,19 +861,315 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131734526</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97471</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stögölen Nord, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569603</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6511533</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135466688</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97471</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stögölen, Stögölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>569598</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6511532</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135466834</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stögölen, Stögölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569614</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6511471</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736327</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734526</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,8 +1195,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135468092</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>92027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135466688</v>
       </c>
       <c r="B5" t="n">
-        <v>97471</v>
+        <v>97515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135466834</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135468092</v>
       </c>
       <c r="B3" t="n">
-        <v>92027</v>
+        <v>92054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135466688</v>
       </c>
       <c r="B5" t="n">
-        <v>97515</v>
+        <v>97542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131734526</v>
+        <v>135468092</v>
       </c>
       <c r="B3" t="n">
-        <v>97471</v>
+        <v>92059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stögölen Nord, Ög</t>
+          <t>Stögölen, Stögölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569603</v>
+        <v>569568</v>
       </c>
       <c r="R3" t="n">
-        <v>6511533</v>
+        <v>6511572</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,22 +871,333 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468092</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131734526</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97471</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stögölen Nord, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569603</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6511533</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131734526</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135466688</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97547</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stögölen, Stögölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>569598</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6511532</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466688</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135466834</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stögölen, Stögölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569614</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6511471</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466834</t>
         </is>
       </c>
     </row>
@@ -894,6 +1205,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135468092</v>
       </c>
       <c r="B3" t="n">
-        <v>92059</v>
+        <v>92061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135466688</v>
       </c>
       <c r="B5" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30829-2026 artfynd.xlsx
+++ b/artfynd/A 30829-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135468092</v>
       </c>
       <c r="B3" t="n">
-        <v>92061</v>
+        <v>92075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135466688</v>
       </c>
       <c r="B5" t="n">
-        <v>97549</v>
+        <v>97566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135466834</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
